--- a/output/pdf_financials_xlsx/DBM.xlsx
+++ b/output/pdf_financials_xlsx/DBM.xlsx
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6.744</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>6.744</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>16.736</v>
+        <v>9.992000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>11.058</v>
+        <v>10.57</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">

--- a/output/pdf_financials_xlsx/DBM.xlsx
+++ b/output/pdf_financials_xlsx/DBM.xlsx
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>4.694</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>7.404</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>12.415</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>14.758</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>18.422</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>55.063</v>
@@ -1552,19 +1552,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>17.099</v>
+        <v>21.793</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>16.959</v>
+        <v>24.363</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>51.908</v>
+        <v>64.32299999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>35.782</v>
+        <v>50.54</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>41.146</v>
+        <v>59.568</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>193.527</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.25144443215514</v>
+        <v>2.869508656059241</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2.056301857692126</v>
+        <v>2.954046946102557</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.305960568171597</v>
+        <v>6.575003884304954</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3.149962586381442</v>
+        <v>4.449139486773186</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.186413639021293</v>
+        <v>4.613043495096008</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>7.608168342326886</v>
@@ -17020,7 +17020,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -17086,7 +17090,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -18584,7 +18588,11 @@
           <t>Depreciation of property, plant and equipment 10 10,909</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -18652,7 +18660,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -20666,7 +20674,11 @@
           <t>Depreciation of property, plant and equipment 10 10,352</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -20734,7 +20746,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -22084,7 +22096,11 @@
           <t>Depreciation of property, plant and equipment 5,315</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E236" s="5" t="n">
         <v>3.527</v>
       </c>
@@ -22152,7 +22168,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E237" s="5" t="n">
